--- a/apps/web/public/templates/clientes-contabilidade-modelo.xlsx
+++ b/apps/web/public/templates/clientes-contabilidade-modelo.xlsx
@@ -160,7 +160,7 @@
     <t>fixo</t>
   </si>
   <si>
-    <t>99888777000166</t>
+    <t>99888777000100</t>
   </si>
   <si>
     <t>contato@saudetotal.com.br</t>
@@ -184,7 +184,7 @@
     <t>Vital Solucoes LTDA</t>
   </si>
   <si>
-    <t>55444333000122</t>
+    <t>55444333000100</t>
   </si>
   <si>
     <t>financeiro@vital.com.br</t>
